--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
